--- a/results/RQ2/analysis_results_formatted.xlsx
+++ b/results/RQ2/analysis_results_formatted.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Análise" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64,27 +64,6 @@
       <bottom style="thin"/>
     </border>
     <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin"/>
@@ -112,6 +91,27 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -127,10 +127,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -517,48 +517,54 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Prática</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Atributo</t>
+          <t>Attribute</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Likert</t>
+          <t>Overall Mean</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Direta vs. Indireta</t>
+          <t>Direct vs. Indirect</t>
         </is>
       </c>
       <c r="E1" s="4" t="n"/>
       <c r="F1" s="4" t="n"/>
-      <c r="G1" s="5" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Grande vs. Pequena</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Large vs. Small</t>
+        </is>
+      </c>
       <c r="J1" s="4" t="n"/>
-      <c r="K1" s="5" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Especialista vs. Não especialista</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="n"/>
-      <c r="N1" s="4" t="n"/>
-      <c r="O1" s="5" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="5" t="n"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Specialist vs. Non-specialist</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="5" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n"/>
@@ -566,12 +572,12 @@
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -581,45 +587,60 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
+          <t>p-value (Holm)</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
           <t>d</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>p-value (Holm)</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>p-value (Holm)</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -628,17 +649,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Análise de Riscos Arquiteturais</t>
+          <t>Architectural Risk Analysis</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -653,52 +674,67 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.397</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>3.07</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2.79</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t>0.347</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>0.124</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
         </is>
       </c>
     </row>
@@ -706,12 +742,12 @@
       <c r="A4" s="7" t="n"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -726,52 +762,67 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4.18</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4.20</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
+          <t>0.633</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4.27</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -779,12 +830,12 @@
       <c r="A5" s="7" t="n"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -797,54 +848,69 @@
           <t>2.00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.051</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0.687</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>(+)**</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2.59</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2.38</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t>0.332</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.233</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>(+)**</t>
         </is>
       </c>
     </row>
@@ -852,7 +918,7 @@
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -872,50 +938,65 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>4.31</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
+          <t>0.731</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4.27</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0.480</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -924,77 +1005,92 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Auditorias de Segurança Externas</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t>0.670</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0.522</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1002,72 +1098,87 @@
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
+          <t>0.443</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>0.296</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1075,72 +1186,87 @@
       <c r="A9" s="7" t="n"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t>0.205</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>(-)*</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>0.043</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.427</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
         </is>
       </c>
     </row>
@@ -1148,70 +1274,85 @@
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3.71</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.188</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0.388</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
@@ -1220,75 +1361,90 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Codificação Segura</t>
+          <t>Emergency Codebase Response</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t>0.741</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>0.237</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>(-)*</t>
         </is>
@@ -1298,72 +1454,87 @@
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0.936</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>0.411</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>4.52</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1371,72 +1542,87 @@
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
+          <t>0.330</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t>(-)*</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3.38</t>
-        </is>
-      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0.187</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
         </is>
       </c>
     </row>
@@ -1444,149 +1630,179 @@
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.908</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
+          <t>0.374</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0.861</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4.46</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Configurações e Gerenciamento de Segurança</t>
+          <t>Identifying Abuse/Misuse Cases</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>0.661</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>(+)**</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>0.601</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.493</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>(+)**</t>
         </is>
       </c>
     </row>
@@ -1594,72 +1810,87 @@
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.830</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4.13</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
+          <t>0.652</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3.79</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0.530</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1898,12 @@
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1682,57 +1913,72 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.049</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>0.687</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>(+)**</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0.783</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.065</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>(+)***</t>
         </is>
       </c>
     </row>
@@ -1740,70 +1986,85 @@
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.632</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>0.896</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -1812,77 +2073,92 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Engenharia de Requisitos de Segurança</t>
+          <t>Manual/Automated Security Testing</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.723</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0.923</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1890,70 +2166,85 @@
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>4.14</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0.268</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>(-)*</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4.24</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>4.06</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>4.41</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0.223</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>(-)*</t>
         </is>
@@ -1963,72 +2254,87 @@
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>2.67</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>(+)***</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0.211</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
+          <t>0.456</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>0.225</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
         </is>
       </c>
     </row>
@@ -2036,149 +2342,179 @@
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.678</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4.56</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0.332</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>4.19</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>4.19</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Execução de Testes Fuzz</t>
+          <t>Monitoring for Security Events</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>(+)**</t>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0.979</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>0.546</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2186,70 +2522,85 @@
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.866</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>0.454</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -2259,72 +2610,87 @@
       <c r="A25" s="7" t="n"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>(+)**</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
+          <t>0.120</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>0.881</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2332,147 +2698,177 @@
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0.802</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>0.181</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Gerenciamento de Riscos</t>
+          <t>Penetration Testing</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.915</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.891</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>0.429</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
@@ -2482,72 +2878,87 @@
       <c r="A28" s="7" t="n"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>4.29</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>(+)*</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
+          <t>0.640</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2555,72 +2966,87 @@
       <c r="A29" s="7" t="n"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.064</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>0.703</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>(+)**</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>0.906</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>0.026</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>(+)***</t>
         </is>
       </c>
     </row>
@@ -2628,149 +3054,179 @@
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.708</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.285</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>0.520</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Gerenciamento de Vulnerabilidades</t>
+          <t>Performing Fuzz Testing</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>(+)**</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.379</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>0.628</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -2778,72 +3234,87 @@
       <c r="A32" s="7" t="n"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>4.30</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>0.869</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>0.279</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2851,72 +3322,87 @@
       <c r="A33" s="7" t="n"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>0.289</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>(+)**</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>0.987</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>(+)**</t>
         </is>
       </c>
     </row>
@@ -2924,70 +3410,85 @@
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.739</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.517</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>0.984</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -2996,42 +3497,42 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Identificação de Casos de Abuso/Mau Uso</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>(+)**</t>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>0.591</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -3041,32 +3542,47 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
+          <t>0.834</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>0.372</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -3074,70 +3590,85 @@
       <c r="A36" s="7" t="n"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0.762</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>3.89</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -3147,72 +3678,87 @@
       <c r="A37" s="7" t="n"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>0.325</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0.235</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>(+)**</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -3220,147 +3766,177 @@
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.081</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>0.504</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>4.54</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>0.253</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Modelagem de Ameaças</t>
+          <t>Secure Coding</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>3.23</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
+          <t>0.792</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>0.591</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
@@ -3370,70 +3946,85 @@
       <c r="A40" s="7" t="n"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.832</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>0.509</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0.284</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>(-)*</t>
         </is>
@@ -3443,72 +4034,87 @@
       <c r="A41" s="7" t="n"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>(+)***</t>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>0.593</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>(-)***</t>
+          <t>0.090</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>0.401</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3516,149 +4122,179 @@
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.884</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0.862</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>0.621</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>4.19</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Monitoramento de Eventos de Segurança</t>
+          <t>Security Configuration and Management</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0.218</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>0.988</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>(+)*</t>
         </is>
       </c>
     </row>
@@ -3666,70 +4302,85 @@
       <c r="A44" s="7" t="n"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.732</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0.529</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>4.44</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>4.31</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>4.19</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>4.52</t>
-        </is>
-      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>0.288</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>(-)*</t>
         </is>
@@ -3739,72 +4390,87 @@
       <c r="A45" s="7" t="n"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>0.253</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3812,70 +4478,85 @@
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>0.906</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>0.773</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -3884,77 +4565,92 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Resposta Emergencial ao Código</t>
+          <t>Security Requirements Engineering</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>0.603</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>(-)**</t>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>0.918</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3962,72 +4658,87 @@
       <c r="A48" s="7" t="n"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>0.330</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
+          <t>0.812</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>3.82</t>
-        </is>
-      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>0.465</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4035,72 +4746,87 @@
       <c r="A49" s="7" t="n"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.049</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
+          <t>0.687</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>(+)***</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>0.740</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>0.285</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
         </is>
       </c>
     </row>
@@ -4108,70 +4834,85 @@
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.547</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
+          <t>0.934</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>3.96</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>3.79</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>0.520</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
@@ -4180,77 +4921,92 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Revisão de Código</t>
+          <t>Software Supply Chain Security</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>0.443</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>0.285</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>3.62</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>3.53</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>3.76</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>(-)**</t>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>0.961</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4258,72 +5014,87 @@
       <c r="A52" s="7" t="n"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>0.985</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>4.19</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>0.542</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4331,72 +5102,87 @@
       <c r="A53" s="7" t="n"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.972</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>0.160</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>0.182</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4404,149 +5190,179 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.466</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>0.126</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Segurança da Cadeia de Suprimentos de Software</t>
+          <t>Threat Modeling</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.361</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
+          <t>0.794</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4554,70 +5370,85 @@
       <c r="A56" s="7" t="n"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.431</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>0.695</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -4627,72 +5458,87 @@
       <c r="A57" s="7" t="n"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.479</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>(+)***</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>(-)***</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="R57" s="8" t="inlineStr">
+        <is>
+          <t>(+)***</t>
         </is>
       </c>
     </row>
@@ -4700,149 +5546,179 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.452</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>4.06</t>
-        </is>
-      </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>0.083</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>0.721</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Testes de Penetração</t>
+          <t>Undergoing External Security Audits</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>0.695</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>0.225</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
         </is>
       </c>
     </row>
@@ -4850,7 +5726,7 @@
       <c r="A60" s="7" t="n"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4860,60 +5736,75 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>0.773</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>0.405</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -4923,70 +5814,85 @@
       <c r="A61" s="7" t="n"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>(+)**</t>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>0.970</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>0.610</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
@@ -4996,147 +5902,177 @@
       <c r="A62" s="6" t="n"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.789</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>0.579</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>(+)</t>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>0.530</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Testes de Segurança Manuais/Automatizados</t>
+          <t>Vulnerability Management</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Ease of use</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.792</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>0.981</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>0.690</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -5146,72 +6082,87 @@
       <c r="A64" s="7" t="n"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>efetividade</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>0.697</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
           <t>4.17</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>(+)</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>4.07</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>0.084</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
         <is>
           <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -5219,72 +6170,87 @@
       <c r="A65" s="7" t="n"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>frequência</t>
+          <t>Frequency of use</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
+          <t>0.094</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>(+)**</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>0.277</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.382</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -5292,70 +6258,85 @@
       <c r="A66" s="6" t="n"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>essencialidade</t>
+          <t>Essentiality</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
           <t>4.56</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
+          <t>0.805</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>4.31</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>4.30</t>
-        </is>
-      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>0.798</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -5363,17 +6344,18 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:H1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="D1:G1"/>
     <mergeCell ref="A55:A58"/>
-    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="N1:R1"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="A19:A22"/>
+    <mergeCell ref="I1:M1"/>
     <mergeCell ref="A63:A66"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="A31:A34"/>
@@ -5381,7 +6363,6 @@
     <mergeCell ref="A39:A42"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A59:A62"/>
-    <mergeCell ref="L1:O1"/>
     <mergeCell ref="A35:A38"/>
     <mergeCell ref="A51:A54"/>
     <mergeCell ref="A1:A2"/>
